--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/АГРОПАКТ ЕООД/АГРОПАКТ ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/АГРОПАКТ ЕООД/АГРОПАКТ ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="42">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,6 +61,27 @@
     <t>2026-05-08</t>
   </si>
   <si>
+    <t>2026-05-16</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>2026-05-30</t>
+  </si>
+  <si>
+    <t>1156 Добрич бул. Добруджа</t>
+  </si>
+  <si>
+    <t>1911 O5 Варна</t>
+  </si>
+  <si>
+    <t>1925 HW Trakia, 243 km. Sofia direc</t>
+  </si>
+  <si>
     <t>A1</t>
   </si>
   <si>
@@ -67,7 +91,37 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>14:49</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>14:49:00</t>
+  </si>
+  <si>
+    <t>12:43:00</t>
+  </si>
+  <si>
+    <t>20:02:00</t>
+  </si>
+  <si>
+    <t>11:26:00</t>
+  </si>
+  <si>
+    <t>12:55:00</t>
+  </si>
+  <si>
+    <t>3231615850 3231615850</t>
+  </si>
+  <si>
+    <t>3231982795 3231982795</t>
+  </si>
+  <si>
+    <t>3232203398 3232203398</t>
+  </si>
+  <si>
+    <t>3232483484 3232483484</t>
+  </si>
+  <si>
+    <t>3232637434 3232637434</t>
   </si>
   <si>
     <t>Общи литри по продукт / АГРОПАКТ ЕООД</t>
@@ -491,7 +545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -500,16 +554,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -549,119 +604,301 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>1156</v>
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F2">
         <v>86.39</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2">
         <v>1.47</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>126.99</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.53</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>132.18</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3">
+        <v>86.31</v>
+      </c>
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3">
+        <v>1.49</v>
+      </c>
+      <c r="I3" s="1">
+        <v>128.6</v>
+      </c>
+      <c r="J3">
+        <v>1.54</v>
+      </c>
+      <c r="K3" s="1">
+        <v>132.92</v>
+      </c>
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4">
+        <v>82.15000000000001</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4">
+        <v>1.5</v>
+      </c>
+      <c r="I4" s="1">
+        <v>123.22</v>
+      </c>
+      <c r="J4">
+        <v>1.57</v>
+      </c>
+      <c r="K4" s="1">
+        <v>128.98</v>
+      </c>
+      <c r="L4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
         <v>17</v>
       </c>
-      <c r="L2">
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5">
+        <v>80.91</v>
+      </c>
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5">
+        <v>1.5</v>
+      </c>
+      <c r="I5" s="1">
+        <v>121.36</v>
+      </c>
+      <c r="J5">
+        <v>1.57</v>
+      </c>
+      <c r="K5" s="1">
+        <v>127.03</v>
+      </c>
+      <c r="L5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="M2">
-        <v>79248</v>
+      <c r="N5" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="3" t="s">
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6">
+        <v>1.52</v>
+      </c>
+      <c r="I6" s="1">
+        <v>124.79</v>
+      </c>
+      <c r="J6">
+        <v>1.58</v>
+      </c>
+      <c r="K6" s="1">
+        <v>129.72</v>
+      </c>
+      <c r="L6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>9</v>
-      </c>
+    <row r="9" spans="1:14">
+      <c r="A9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
     </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="6">
-        <v>86.39</v>
-      </c>
-      <c r="C7" s="6">
-        <v>1</v>
-      </c>
-      <c r="D7" s="7">
-        <v>1.47</v>
-      </c>
-      <c r="E7" s="6">
-        <v>126.99</v>
-      </c>
-      <c r="F7" s="6">
-        <v>132.18</v>
+    <row r="10" spans="1:14">
+      <c r="A10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="9">
-        <v>86.39</v>
-      </c>
-      <c r="C8" s="9">
-        <v>1</v>
-      </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="9">
-        <v>126.99</v>
-      </c>
-      <c r="F8" s="9">
-        <v>132.18</v>
+    <row r="11" spans="1:14">
+      <c r="A11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="6">
+        <v>417.86</v>
+      </c>
+      <c r="C11" s="6">
+        <v>5</v>
+      </c>
+      <c r="D11" s="7">
+        <v>1.4956</v>
+      </c>
+      <c r="E11" s="6">
+        <v>624.96</v>
+      </c>
+      <c r="F11" s="6">
+        <v>650.83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="9">
+        <v>417.86</v>
+      </c>
+      <c r="C12" s="9">
+        <v>5</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="9">
+        <v>624.96</v>
+      </c>
+      <c r="F12" s="9">
+        <v>650.83</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/АГРОПАКТ ЕООД/АГРОПАКТ ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/АГРОПАКТ ЕООД/АГРОПАКТ ЕООД.xlsx
@@ -175,7 +175,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -185,12 +185,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -240,17 +234,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/АГРОПАКТ ЕООД/АГРОПАКТ ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/АГРОПАКТ ЕООД/АГРОПАКТ ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,37 +46,13 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
-    <t>Час</t>
-  </si>
-  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-05-16</t>
-  </si>
-  <si>
-    <t>2026-05-21</t>
-  </si>
-  <si>
-    <t>2026-05-27</t>
-  </si>
-  <si>
-    <t>2026-05-30</t>
-  </si>
-  <si>
-    <t>1156 Добрич бул. Добруджа</t>
-  </si>
-  <si>
-    <t>1911 O5 Варна</t>
-  </si>
-  <si>
-    <t>1925 HW Trakia, 243 km. Sofia direc</t>
+    <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>Тракия Езеро</t>
   </si>
   <si>
     <t>A1</t>
@@ -89,39 +62,6 @@
   </si>
   <si>
     <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>14:49:00</t>
-  </si>
-  <si>
-    <t>12:43:00</t>
-  </si>
-  <si>
-    <t>20:02:00</t>
-  </si>
-  <si>
-    <t>11:26:00</t>
-  </si>
-  <si>
-    <t>12:55:00</t>
-  </si>
-  <si>
-    <t>3231615850 3231615850</t>
-  </si>
-  <si>
-    <t>3231982795 3231982795</t>
-  </si>
-  <si>
-    <t>3232203398 3232203398</t>
-  </si>
-  <si>
-    <t>3232483484 3232483484</t>
-  </si>
-  <si>
-    <t>3232637434 3232637434</t>
   </si>
   <si>
     <t>Общи литри по продукт / АГРОПАКТ ЕООД</t>
@@ -539,7 +479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -548,17 +488,14 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -592,307 +529,113 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="C2" t="s">
         <v>13</v>
       </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2">
+        <v>87.70999999999999</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H2">
+        <v>133.32</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="J2">
+        <v>137.7</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="5" spans="1:11">
+      <c r="A5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2">
-        <v>86.39</v>
-      </c>
-      <c r="G2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2">
-        <v>1.47</v>
-      </c>
-      <c r="I2" s="1">
-        <v>126.99</v>
-      </c>
-      <c r="J2">
-        <v>1.53</v>
-      </c>
-      <c r="K2" s="1">
-        <v>132.18</v>
-      </c>
-      <c r="L2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>31</v>
+      <c r="D6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
+    <row r="7" spans="1:11">
+      <c r="A7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3">
-        <v>86.31</v>
-      </c>
-      <c r="G3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3">
-        <v>1.49</v>
-      </c>
-      <c r="I3" s="1">
-        <v>128.6</v>
-      </c>
-      <c r="J3">
-        <v>1.54</v>
-      </c>
-      <c r="K3" s="1">
-        <v>132.92</v>
-      </c>
-      <c r="L3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>32</v>
+      <c r="B7" s="6">
+        <v>87.70999999999999</v>
+      </c>
+      <c r="C7" s="6">
+        <v>1</v>
+      </c>
+      <c r="D7" s="7">
+        <v>1.52</v>
+      </c>
+      <c r="E7" s="6">
+        <v>133.32</v>
+      </c>
+      <c r="F7" s="6">
+        <v>137.7</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4">
-        <v>82.15000000000001</v>
-      </c>
-      <c r="G4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4">
-        <v>1.5</v>
-      </c>
-      <c r="I4" s="1">
-        <v>123.22</v>
-      </c>
-      <c r="J4">
-        <v>1.57</v>
-      </c>
-      <c r="K4" s="1">
-        <v>128.98</v>
-      </c>
-      <c r="L4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5">
-        <v>80.91</v>
-      </c>
-      <c r="G5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5">
-        <v>1.5</v>
-      </c>
-      <c r="I5" s="1">
-        <v>121.36</v>
-      </c>
-      <c r="J5">
-        <v>1.57</v>
-      </c>
-      <c r="K5" s="1">
-        <v>127.03</v>
-      </c>
-      <c r="L5" t="s">
-        <v>29</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
+    <row r="8" spans="1:11">
+      <c r="A8" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="G6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6">
-        <v>1.52</v>
-      </c>
-      <c r="I6" s="1">
-        <v>124.79</v>
-      </c>
-      <c r="J6">
-        <v>1.58</v>
-      </c>
-      <c r="K6" s="1">
-        <v>129.72</v>
-      </c>
-      <c r="L6" t="s">
-        <v>30</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="6">
-        <v>417.86</v>
-      </c>
-      <c r="C11" s="6">
-        <v>5</v>
-      </c>
-      <c r="D11" s="7">
-        <v>1.4956</v>
-      </c>
-      <c r="E11" s="6">
-        <v>624.96</v>
-      </c>
-      <c r="F11" s="6">
-        <v>650.83</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="9">
-        <v>417.86</v>
-      </c>
-      <c r="C12" s="9">
-        <v>5</v>
-      </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="9">
-        <v>624.96</v>
-      </c>
-      <c r="F12" s="9">
-        <v>650.83</v>
+      <c r="B8" s="9">
+        <v>87.70999999999999</v>
+      </c>
+      <c r="C8" s="9">
+        <v>1</v>
+      </c>
+      <c r="D8" s="7"/>
+      <c r="E8" s="9">
+        <v>133.32</v>
+      </c>
+      <c r="F8" s="9">
+        <v>137.7</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A5:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/АГРОПАКТ ЕООД/АГРОПАКТ ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/АГРОПАКТ ЕООД/АГРОПАКТ ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="35">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,6 +52,12 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-13</t>
   </si>
   <si>
@@ -58,10 +67,10 @@
     <t>2026-06-22</t>
   </si>
   <si>
-    <t>Тракия Езеро</t>
-  </si>
-  <si>
-    <t>Добрич Добруджа</t>
+    <t>1195 243 Тракия Езеро</t>
+  </si>
+  <si>
+    <t>1156 Добрич бул. Добруджа</t>
   </si>
   <si>
     <t>A1</t>
@@ -73,13 +82,25 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2026-06-13 15:31:31</t>
-  </si>
-  <si>
-    <t>2026-06-17 13:16:53</t>
-  </si>
-  <si>
-    <t>2026-06-22 11:21:32</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>15:30:00</t>
+  </si>
+  <si>
+    <t>13:16:00</t>
+  </si>
+  <si>
+    <t>11:21:00</t>
+  </si>
+  <si>
+    <t>3233301652 3233301652</t>
+  </si>
+  <si>
+    <t>3233492845 3233492845</t>
+  </si>
+  <si>
+    <t>3233730474 3233730474</t>
   </si>
   <si>
     <t>Общи литри по продукт / АГРОПАКТ ЕООД</t>
@@ -497,7 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -506,14 +527,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -547,115 +571,151 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F2">
         <v>87.70999999999999</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2">
         <v>1.48</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>129.81</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.57</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>137.7</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F3">
         <v>88.55</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3">
         <v>1.46</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>129.28</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.55</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>137.25</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F4">
         <v>93.91</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4">
         <v>1.43</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>134.29</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.51</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>141.8</v>
       </c>
-      <c r="K4" t="s">
-        <v>21</v>
+      <c r="L4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:14">
       <c r="A7" s="3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -663,29 +723,29 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:14">
       <c r="A8" s="4" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:14">
       <c r="A9" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B9" s="6">
         <v>270.17</v>
@@ -703,9 +763,9 @@
         <v>416.75</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:14">
       <c r="A10" s="8" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B10" s="9">
         <v>270.17</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/АГРОПАКТ ЕООД/АГРОПАКТ ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/АГРОПАКТ ЕООД/АГРОПАКТ ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="48">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-03</t>
   </si>
   <si>
@@ -61,10 +67,25 @@
     <t>2026-07-13</t>
   </si>
   <si>
-    <t>Добрич Добруджа</t>
-  </si>
-  <si>
-    <t>В.Търново</t>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>1156 Добрич бул. Добруджа</t>
+  </si>
+  <si>
+    <t>1103 Велико Търново изход</t>
+  </si>
+  <si>
+    <t>1925 HW Trakia, 243 km. Sofia direc</t>
   </si>
   <si>
     <t>A1</t>
@@ -76,13 +97,49 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2026-07-03 15:23:28</t>
-  </si>
-  <si>
-    <t>2026-07-09 18:47:53</t>
-  </si>
-  <si>
-    <t>2026-07-13 12:54:39</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>15:23:00</t>
+  </si>
+  <si>
+    <t>18:49:00</t>
+  </si>
+  <si>
+    <t>12:54:00</t>
+  </si>
+  <si>
+    <t>12:55:00</t>
+  </si>
+  <si>
+    <t>17:08:00</t>
+  </si>
+  <si>
+    <t>14:45:00</t>
+  </si>
+  <si>
+    <t>14:21:00</t>
+  </si>
+  <si>
+    <t>3234270400 3234270400</t>
+  </si>
+  <si>
+    <t>3234552582 3234552582</t>
+  </si>
+  <si>
+    <t>3234752195 3234752195</t>
+  </si>
+  <si>
+    <t>3235007386 3235007386</t>
+  </si>
+  <si>
+    <t>3235254240 3235254240</t>
+  </si>
+  <si>
+    <t>3235447687 3235447687</t>
+  </si>
+  <si>
+    <t>3235538457 3235538457</t>
   </si>
   <si>
     <t>Общи литри по продукт / АГРОПАКТ ЕООД</t>
@@ -500,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -509,15 +566,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -554,192 +613,392 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F2">
         <v>90.33</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2">
         <v>1.4</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>126.46</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.5</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>135.5</v>
       </c>
-      <c r="K2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2">
+      <c r="L2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="N2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F3">
         <v>84.2</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3">
         <v>1.4</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>117.88</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.48</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>124.62</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
         <v>21</v>
       </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F4">
         <v>93.23999999999999</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4">
         <v>1.4</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>130.54</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.49</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>138.93</v>
       </c>
-      <c r="K4" t="s">
-        <v>22</v>
-      </c>
-      <c r="L4">
+      <c r="L4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="3" t="s">
+      <c r="N4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5">
+        <v>81.36</v>
+      </c>
+      <c r="G5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5">
+        <v>1.42</v>
+      </c>
+      <c r="I5" s="1">
+        <v>115.53</v>
+      </c>
+      <c r="J5">
+        <v>1.52</v>
+      </c>
+      <c r="K5" s="1">
+        <v>123.67</v>
+      </c>
+      <c r="L5" t="s">
+        <v>31</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6">
+        <v>86.87</v>
+      </c>
+      <c r="G6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6">
+        <v>1.44</v>
+      </c>
+      <c r="I6" s="1">
+        <v>125.09</v>
+      </c>
+      <c r="J6">
+        <v>1.52</v>
+      </c>
+      <c r="K6" s="1">
+        <v>132.04</v>
+      </c>
+      <c r="L6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7">
+        <v>89.48</v>
+      </c>
+      <c r="G7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7">
+        <v>1.44</v>
+      </c>
+      <c r="I7" s="1">
+        <v>128.85</v>
+      </c>
+      <c r="J7">
+        <v>1.55</v>
+      </c>
+      <c r="K7" s="1">
+        <v>138.69</v>
+      </c>
+      <c r="L7" t="s">
+        <v>33</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="4" t="s">
+      <c r="C8" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="D8" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="E8" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="F8">
+        <v>81.12</v>
+      </c>
+      <c r="G8" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="H8">
+        <v>1.49</v>
+      </c>
+      <c r="I8" s="1">
+        <v>120.87</v>
+      </c>
+      <c r="J8">
+        <v>1.58</v>
+      </c>
+      <c r="K8" s="1">
+        <v>128.17</v>
+      </c>
+      <c r="L8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="6">
+        <v>606.6</v>
+      </c>
+      <c r="C13" s="6">
         <v>7</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="6">
-        <v>267.77</v>
-      </c>
-      <c r="C9" s="6">
-        <v>3</v>
-      </c>
-      <c r="D9" s="7">
-        <v>1.4</v>
-      </c>
-      <c r="E9" s="6">
-        <v>374.88</v>
-      </c>
-      <c r="F9" s="6">
-        <v>399.05</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="9">
-        <v>267.77</v>
-      </c>
-      <c r="C10" s="9">
-        <v>3</v>
-      </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="9">
-        <v>374.88</v>
-      </c>
-      <c r="F10" s="9">
-        <v>399.05</v>
+      <c r="D13" s="7">
+        <v>1.4263</v>
+      </c>
+      <c r="E13" s="6">
+        <v>865.22</v>
+      </c>
+      <c r="F13" s="6">
+        <v>921.62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="9">
+        <v>606.6</v>
+      </c>
+      <c r="C14" s="9">
+        <v>7</v>
+      </c>
+      <c r="D14" s="7"/>
+      <c r="E14" s="9">
+        <v>865.22</v>
+      </c>
+      <c r="F14" s="9">
+        <v>921.62</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A11:F11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/АГРОПАКТ ЕООД/АГРОПАКТ ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/АГРОПАКТ ЕООД/АГРОПАКТ ЕООД.xlsx
@@ -166,7 +166,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -969,7 +969,7 @@
         <v>7</v>
       </c>
       <c r="D13" s="7">
-        <v>1.4263</v>
+        <v>1.426344</v>
       </c>
       <c r="E13" s="6">
         <v>865.22</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/АГРОПАКТ ЕООД/АГРОПАКТ ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/АГРОПАКТ ЕООД/АГРОПАКТ ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="49">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -557,7 +560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -570,13 +573,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -619,318 +622,342 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2">
+        <v>90.333</v>
+      </c>
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2">
+        <v>1.359</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.399</v>
+      </c>
+      <c r="J2">
+        <v>126.375867</v>
+      </c>
+      <c r="K2" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="L2" s="1">
+        <v>135.4995</v>
+      </c>
+      <c r="M2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3">
+        <v>84.203</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3">
+        <v>1.359</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.399</v>
+      </c>
+      <c r="J3">
+        <v>117.799997</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="L3" s="1">
+        <v>124.62044</v>
+      </c>
+      <c r="M3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4">
+        <v>93.242</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4">
+        <v>1.359</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.399</v>
+      </c>
+      <c r="J4">
+        <v>130.445558</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="L4" s="1">
+        <v>138.93058</v>
+      </c>
+      <c r="M4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5">
+        <v>81.36199999999999</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5">
+        <v>1.379</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.419</v>
+      </c>
+      <c r="J5">
+        <v>115.452678</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="L5" s="1">
+        <v>123.67024</v>
+      </c>
+      <c r="M5" t="s">
+        <v>32</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6">
+        <v>86.86799999999999</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6">
+        <v>1.401</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.441</v>
+      </c>
+      <c r="J6">
+        <v>125.176788</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="L6" s="1">
+        <v>132.03936</v>
+      </c>
+      <c r="M6" t="s">
+        <v>33</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7">
+        <v>89.48399999999999</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7">
+        <v>1.401</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1.441</v>
+      </c>
+      <c r="J7">
+        <v>128.946444</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="L7" s="1">
+        <v>138.7002</v>
+      </c>
+      <c r="M7" t="s">
+        <v>34</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" t="s">
         <v>21</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B8" t="s">
         <v>24</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C8" t="s">
         <v>25</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D8" t="s">
         <v>26</v>
       </c>
-      <c r="F2">
-        <v>90.33</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="E8" t="s">
         <v>27</v>
-      </c>
-      <c r="H2">
-        <v>1.4</v>
-      </c>
-      <c r="I2" s="1">
-        <v>126.46</v>
-      </c>
-      <c r="J2">
-        <v>1.5</v>
-      </c>
-      <c r="K2" s="1">
-        <v>135.5</v>
-      </c>
-      <c r="L2" t="s">
-        <v>28</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3">
-        <v>84.2</v>
-      </c>
-      <c r="G3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3">
-        <v>1.4</v>
-      </c>
-      <c r="I3" s="1">
-        <v>117.88</v>
-      </c>
-      <c r="J3">
-        <v>1.48</v>
-      </c>
-      <c r="K3" s="1">
-        <v>124.62</v>
-      </c>
-      <c r="L3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4">
-        <v>93.23999999999999</v>
-      </c>
-      <c r="G4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4">
-        <v>1.4</v>
-      </c>
-      <c r="I4" s="1">
-        <v>130.54</v>
-      </c>
-      <c r="J4">
-        <v>1.49</v>
-      </c>
-      <c r="K4" s="1">
-        <v>138.93</v>
-      </c>
-      <c r="L4" t="s">
-        <v>30</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5">
-        <v>81.36</v>
-      </c>
-      <c r="G5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5">
-        <v>1.42</v>
-      </c>
-      <c r="I5" s="1">
-        <v>115.53</v>
-      </c>
-      <c r="J5">
-        <v>1.52</v>
-      </c>
-      <c r="K5" s="1">
-        <v>123.67</v>
-      </c>
-      <c r="L5" t="s">
-        <v>31</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6">
-        <v>86.87</v>
-      </c>
-      <c r="G6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6">
-        <v>1.44</v>
-      </c>
-      <c r="I6" s="1">
-        <v>125.09</v>
-      </c>
-      <c r="J6">
-        <v>1.52</v>
-      </c>
-      <c r="K6" s="1">
-        <v>132.04</v>
-      </c>
-      <c r="L6" t="s">
-        <v>32</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7">
-        <v>89.48</v>
-      </c>
-      <c r="G7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7">
-        <v>1.44</v>
-      </c>
-      <c r="I7" s="1">
-        <v>128.85</v>
-      </c>
-      <c r="J7">
-        <v>1.55</v>
-      </c>
-      <c r="K7" s="1">
-        <v>138.69</v>
-      </c>
-      <c r="L7" t="s">
-        <v>33</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" t="s">
-        <v>26</v>
       </c>
       <c r="F8">
         <v>81.12</v>
       </c>
       <c r="G8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H8">
-        <v>1.49</v>
+        <v>1.449</v>
       </c>
       <c r="I8" s="1">
-        <v>120.87</v>
+        <v>1.489</v>
       </c>
       <c r="J8">
+        <v>120.78768</v>
+      </c>
+      <c r="K8" s="1">
         <v>1.58</v>
       </c>
-      <c r="K8" s="1">
-        <v>128.17</v>
-      </c>
-      <c r="L8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M8">
+      <c r="L8" s="1">
+        <v>128.1696</v>
+      </c>
+      <c r="M8" t="s">
+        <v>35</v>
+      </c>
+      <c r="N8">
         <v>0</v>
       </c>
-      <c r="N8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -938,62 +965,62 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:15">
       <c r="A12" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B13" s="6">
-        <v>606.6</v>
+        <v>606.612</v>
       </c>
       <c r="C13" s="6">
         <v>7</v>
       </c>
       <c r="D13" s="7">
-        <v>1.426344</v>
+        <v>1.425928</v>
       </c>
       <c r="E13" s="6">
-        <v>865.22</v>
+        <v>864.99</v>
       </c>
       <c r="F13" s="6">
-        <v>921.62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+        <v>921.63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" s="9">
-        <v>606.6</v>
+        <v>606.612</v>
       </c>
       <c r="C14" s="9">
         <v>7</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="9">
-        <v>865.22</v>
+        <v>864.99</v>
       </c>
       <c r="F14" s="9">
-        <v>921.62</v>
+        <v>921.63</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/АГРОПАКТ ЕООД/АГРОПАКТ ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/АГРОПАКТ ЕООД/АГРОПАКТ ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="48">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -168,8 +165,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -262,10 +259,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -560,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -573,13 +570,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -622,342 +619,318 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
         <v>25</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>26</v>
-      </c>
-      <c r="E2" t="s">
-        <v>27</v>
       </c>
       <c r="F2">
         <v>90.333</v>
       </c>
       <c r="G2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2">
+        <v>1.399</v>
+      </c>
+      <c r="I2" s="1">
+        <v>126.376</v>
+      </c>
+      <c r="J2">
+        <v>1.5</v>
+      </c>
+      <c r="K2" s="1">
+        <v>135.5</v>
+      </c>
+      <c r="L2" t="s">
         <v>28</v>
       </c>
-      <c r="H2">
-        <v>1.359</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.399</v>
-      </c>
-      <c r="J2">
-        <v>126.375867</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L2" s="1">
-        <v>135.4995</v>
-      </c>
-      <c r="M2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="O2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
         <v>25</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>27</v>
       </c>
       <c r="F3">
         <v>84.203</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H3">
-        <v>1.359</v>
+        <v>1.399</v>
       </c>
       <c r="I3" s="1">
-        <v>1.399</v>
+        <v>117.8</v>
       </c>
       <c r="J3">
-        <v>117.799997</v>
+        <v>1.48</v>
       </c>
       <c r="K3" s="1">
-        <v>1.48</v>
-      </c>
-      <c r="L3" s="1">
-        <v>124.62044</v>
-      </c>
-      <c r="M3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N3">
+        <v>124.62</v>
+      </c>
+      <c r="L3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
         <v>25</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>27</v>
       </c>
       <c r="F4">
         <v>93.242</v>
       </c>
       <c r="G4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H4">
-        <v>1.359</v>
+        <v>1.399</v>
       </c>
       <c r="I4" s="1">
-        <v>1.399</v>
+        <v>130.446</v>
       </c>
       <c r="J4">
-        <v>130.445558</v>
+        <v>1.49</v>
       </c>
       <c r="K4" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L4" s="1">
-        <v>138.93058</v>
-      </c>
-      <c r="M4" t="s">
-        <v>31</v>
-      </c>
-      <c r="N4">
+        <v>138.931</v>
+      </c>
+      <c r="L4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="O4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
         <v>25</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>26</v>
-      </c>
-      <c r="E5" t="s">
-        <v>27</v>
       </c>
       <c r="F5">
         <v>81.36199999999999</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H5">
-        <v>1.379</v>
+        <v>1.419</v>
       </c>
       <c r="I5" s="1">
-        <v>1.419</v>
+        <v>115.453</v>
       </c>
       <c r="J5">
-        <v>115.452678</v>
+        <v>1.52</v>
       </c>
       <c r="K5" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L5" s="1">
-        <v>123.67024</v>
-      </c>
-      <c r="M5" t="s">
-        <v>32</v>
-      </c>
-      <c r="N5">
+        <v>123.67</v>
+      </c>
+      <c r="L5" t="s">
+        <v>31</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="O5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
         <v>25</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>26</v>
-      </c>
-      <c r="E6" t="s">
-        <v>27</v>
       </c>
       <c r="F6">
         <v>86.86799999999999</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H6">
-        <v>1.401</v>
+        <v>1.441</v>
       </c>
       <c r="I6" s="1">
-        <v>1.441</v>
+        <v>125.177</v>
       </c>
       <c r="J6">
-        <v>125.176788</v>
+        <v>1.52</v>
       </c>
       <c r="K6" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L6" s="1">
-        <v>132.03936</v>
-      </c>
-      <c r="M6" t="s">
-        <v>33</v>
-      </c>
-      <c r="N6">
+        <v>132.039</v>
+      </c>
+      <c r="L6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
-      <c r="O6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="N6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
         <v>25</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>26</v>
-      </c>
-      <c r="E7" t="s">
-        <v>27</v>
       </c>
       <c r="F7">
         <v>89.48399999999999</v>
       </c>
       <c r="G7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H7">
-        <v>1.401</v>
+        <v>1.441</v>
       </c>
       <c r="I7" s="1">
-        <v>1.441</v>
+        <v>128.946</v>
       </c>
       <c r="J7">
-        <v>128.946444</v>
+        <v>1.55</v>
       </c>
       <c r="K7" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L7" s="1">
-        <v>138.7002</v>
-      </c>
-      <c r="M7" t="s">
-        <v>34</v>
-      </c>
-      <c r="N7">
+        <v>138.7</v>
+      </c>
+      <c r="L7" t="s">
+        <v>33</v>
+      </c>
+      <c r="M7">
         <v>0</v>
       </c>
-      <c r="O7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="N7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
         <v>24</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>25</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>26</v>
-      </c>
-      <c r="E8" t="s">
-        <v>27</v>
       </c>
       <c r="F8">
         <v>81.12</v>
       </c>
       <c r="G8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H8">
-        <v>1.449</v>
+        <v>1.489</v>
       </c>
       <c r="I8" s="1">
-        <v>1.489</v>
+        <v>120.788</v>
       </c>
       <c r="J8">
-        <v>120.78768</v>
+        <v>1.58</v>
       </c>
       <c r="K8" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="L8" s="1">
-        <v>128.1696</v>
-      </c>
-      <c r="M8" t="s">
-        <v>35</v>
-      </c>
-      <c r="N8">
+        <v>128.17</v>
+      </c>
+      <c r="L8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M8">
         <v>0</v>
       </c>
-      <c r="O8" t="s">
+      <c r="N8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="3" t="s">
         <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
-      <c r="A11" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -965,49 +938,49 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:14">
       <c r="A12" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="C12" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>47</v>
-      </c>
       <c r="E12" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B13" s="6">
         <v>606.612</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="7">
         <v>7</v>
       </c>
       <c r="D13" s="7">
-        <v>1.425928</v>
-      </c>
-      <c r="E13" s="6">
-        <v>864.99</v>
-      </c>
-      <c r="F13" s="6">
+        <v>1.426</v>
+      </c>
+      <c r="E13" s="7">
+        <v>864.986</v>
+      </c>
+      <c r="F13" s="7">
         <v>921.63</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:14">
       <c r="A14" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B14" s="9">
         <v>606.612</v>
@@ -1017,7 +990,7 @@
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="9">
-        <v>864.99</v>
+        <v>864.986</v>
       </c>
       <c r="F14" s="9">
         <v>921.63</v>
